--- a/수련지도_입력양식_신경과.xlsx
+++ b/수련지도_입력양식_신경과.xlsx
@@ -182,7 +182,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -264,6 +264,14 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -696,7 +704,7 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" s="21">
-      <c r="A3" s="23" t="n"/>
+      <c r="A3" s="28" t="n"/>
       <c r="B3" s="7" t="n">
         <v>2</v>
       </c>
@@ -712,7 +720,7 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" s="21">
-      <c r="A4" s="23" t="n"/>
+      <c r="A4" s="28" t="n"/>
       <c r="B4" s="7" t="n">
         <v>3</v>
       </c>
@@ -728,7 +736,7 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" s="21">
-      <c r="A5" s="23" t="n"/>
+      <c r="A5" s="28" t="n"/>
       <c r="B5" s="7" t="n">
         <v>4</v>
       </c>
@@ -744,7 +752,7 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" s="21">
-      <c r="A6" s="24" t="n"/>
+      <c r="A6" s="29" t="n"/>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
@@ -783,7 +791,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="21">
-      <c r="A8" s="23" t="n"/>
+      <c r="A8" s="28" t="n"/>
       <c r="B8" s="7" t="n">
         <v>2</v>
       </c>
@@ -799,7 +807,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="21">
-      <c r="A9" s="23" t="n"/>
+      <c r="A9" s="28" t="n"/>
       <c r="B9" s="7" t="n">
         <v>3</v>
       </c>
@@ -815,7 +823,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="21">
-      <c r="A10" s="23" t="n"/>
+      <c r="A10" s="28" t="n"/>
       <c r="B10" s="7" t="n">
         <v>4</v>
       </c>
@@ -831,7 +839,7 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" s="21">
-      <c r="A11" s="24" t="n"/>
+      <c r="A11" s="29" t="n"/>
       <c r="B11" s="1" t="n">
         <v>5</v>
       </c>
@@ -870,7 +878,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="21">
-      <c r="A13" s="23" t="n"/>
+      <c r="A13" s="28" t="n"/>
       <c r="B13" s="7" t="n">
         <v>2</v>
       </c>
@@ -886,7 +894,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" s="21">
-      <c r="A14" s="23" t="n"/>
+      <c r="A14" s="28" t="n"/>
       <c r="B14" s="7" t="n">
         <v>3</v>
       </c>
@@ -902,7 +910,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="21">
-      <c r="A15" s="23" t="n"/>
+      <c r="A15" s="28" t="n"/>
       <c r="B15" s="7" t="n">
         <v>4</v>
       </c>
@@ -918,7 +926,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="21">
-      <c r="A16" s="24" t="n"/>
+      <c r="A16" s="29" t="n"/>
       <c r="B16" s="1" t="n">
         <v>5</v>
       </c>
@@ -955,7 +963,7 @@
     <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
     <col width="22" customWidth="1" style="21" min="3" max="3"/>
     <col width="20.75" customWidth="1" style="21" min="4" max="4"/>
-    <col width="80" customWidth="1" style="21" min="5" max="5"/>
+    <col width="85" customWidth="1" style="21" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="21">
@@ -985,7 +993,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="190" customHeight="1" s="21">
+    <row r="2" ht="159" customHeight="1" s="21">
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>책임 지도전문의</t>
@@ -1006,22 +1014,21 @@
           <t>26.07.01~</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
-        <is>
-          <t>7월 수련지도 : 15건 (현장 교육 7, 임상 교육 2, 환자 교육 1, 이론 교육 5)
-7월 간담회 : 1건
-7월 개별 면담 : 4건 (분야별: 수련·근무 2, 학습·역량 3, 진로·진학 1)
-8월 수련지도 : 6건 (현장 교육 4, 이론 교육 2)
-8월 개별 면담 : 2건 (분야별: 수련·근무 1, 생활·심리 1, 기타 1)
-9월 수련지도 : 13건 (현장 교육 5, 임상 교육 3, 이론 교육 5)
-9월 학술집담회 : 1건
-9월 간담회 : 2건
-9월 개별 면담 : 4건 (분야별: 수련·근무 3, 학습·역량 1, 진로·진학 1)
-합계 : 48건</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="76" customHeight="1" s="21">
+      <c r="E2" s="30" t="inlineStr">
+        <is>
+          <t>7월 간담회 : 2학기 스케줄·휴가 조정(송준규, 박예지, 유홍근)
+7월 면담 : 수련·학습·진로 상담(송준규, 박예지, 박은지, 유홍근)
+7월 수련지도 : 전공의 강의, 외래·응급실 진료지도, 치매안심센터 진료(송준규, 박예지, 박은지, 유홍근)
+8월 면담 : 수련 고충·의정사태 이후 상황 상담(송준규, 박예지, 박은지, 유홍근)
+8월 수련지도 : 외래·응급실 진료지도, 뇌혈관 해부 강의, 뇌졸중 증례 논의(송준규, 박예지, 박은지, 유홍근)
+9월 학술집담회 : 원내 컨퍼런스 증례 발표(박은지, 신정욱)
+9월 간담회 : 2학기 학회 참석·원내 학술활동 일정 논의(박은지, 신정욱)
+9월 면담 : 수련·진로·당직 고충 상담(박은지, 신정욱)
+9월 수련지도 : 외래·응급실 진료지도, 치매안심센터 진료, 척수·NMOSD 강의(박은지, 유홍근, 신정욱)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="57" customHeight="1" s="21">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1042,12 +1049,11 @@
           <t>26.07.01~</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>7월 수련지도 : 6건 (임상 교육 4, 이론 교육 2)
-8월 수련지도 : 4건 (임상 교육 2, 이론 교육 2)
-9월 수련지도 : 4건 (임상 교육 3, 이론 교육 1)
-합계 : 14건</t>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>7월 수련지도 : 신경생리검사 판독 교육, Preston 북리딩(송준규, 박예지, 박은지, 유홍근)
+8월 수련지도 : 신경생리검사 판독 교육, Preston 북리딩(송준규, 박예지, 박은지, 유홍근)
+9월 수련지도 : 신경생리검사 판독 교육, Preston 북리딩(박은지, 신정욱)</t>
         </is>
       </c>
     </row>
